--- a/2022/Mount2/Mount2_Members_final.xlsx
+++ b/2022/Mount2/Mount2_Members_final.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
